--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,10 +568,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3">
-        <f>HYPERLINK("C:\Users\User\Jobs\data\tailored_outputs\InternGenAIProgramfmdinFrankfurtGermany60323ITEntwicklungatAllianz_CL.md", "Letter")</f>
-        <v/>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
@@ -594,11 +591,548 @@
           <t>https://linkedin.com/in/birgit-braun-79a1a918a</t>
         </is>
       </c>
-      <c r="O3">
-        <f>HYPERLINK("C:\Users\User\Jobs\data\tailored_outputs\InternGenAIProgramfmdinFrankfurtGermany60323ITEntwicklungatAllianz_CV.pdf", "PDF")</f>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>recruiting.ger@siemens.com</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) AI Agents &amp; Financial Data Engineering</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>recruiting.ger@siemens.com</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) Support Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>recruiting.ger@siemens.com</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BMW Group</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Werkstudent Data Science und Data Engineering (m/w/x)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>recruiting@company.com</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DATEV (Partner of local tech ecosystem)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Werkstudent Data Science &amp; Machine Learning (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>recruiting@company.com</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BMW Group</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Werkstudent Data Science und Data Engineering (m/w/x)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>recruiting@company.com</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Deloitte (Consulting for requested firms)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Werkstudent AI &amp; Data Engineering</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>recruiting@company.com</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>recruiting.ger@siemens.com</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unknown_Job</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ready (Manual)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Siemens AG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ready (Manual)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Siemens AG</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16">
+        <f>HYPERLINK("C:\Users\User\Jobs\data\tailored_outputs\WorkingStudentfmdAdvancedAnalyticsandArtificialIntelligence\Cover_Letter.pdf", "Letter")</f>
         <v/>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Ready (Manual)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Hiring Team</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16">
+        <f>HYPERLINK("C:\Users\User\Jobs\data\tailored_outputs\WorkingStudentfmdAdvancedAnalyticsandArtificialIntelligence\Tailored_CV.pdf", "PDF")</f>
+        <v/>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/data/tracking.xlsx
+++ b/data/tracking.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -441,575 +441,413 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Contact Name</t>
+          <t>Tailored_Files</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Contact Email</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Contact LinkedIn</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Resume PDF</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Cover Letter</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Outreach</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Job URL</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Contact Person</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Resume</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Gmail Link</t>
+          <t>Post_Mortem</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Join Allianz: Explore Career Opportunities</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Intern GenAI Program (f/m/d) in Frankfurt, Germany, 60323 | IT &amp; Entwicklung at Allianz</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Birgit Braun</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>birgit.braun@allianz.com</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/birgit-braun-79a1a918a</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>recruiting.ger@siemens.com</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WerkstudentArtificialIntelligence</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Working Student (f/m/d) AI Agents &amp; Financial Data Engineering</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>recruiting.ger@siemens.com</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WerkstudentArtificialIntelligence</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WerkstudentDataAnalytics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Working Student (f/m/d) Support Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>recruiting.ger@siemens.com</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WerkstudentDataAnalytics</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WerkstudentDataAnalyticsBusinessIntelligence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Werkstudent Data Science und Data Engineering (m/w/x)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>recruiting@company.com</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WerkstudentDataAnalyticsBusinessIntelligence</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WerkstudentDatenbankerstellungUndVerarbeitung</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DATEV (Partner of local tech ecosystem)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Werkstudent Data Science &amp; Machine Learning (m/w/d)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>recruiting@company.com</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WerkstudentDatenbankerstellungUndVerarbeitung</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WerkstudentDigitalisierungKIimProjektmanagement</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Werkstudent Data Science und Data Engineering (m/w/x)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>recruiting@company.com</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WerkstudentDigitalisierungKIimProjektmanagement</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WerkstudentKünstlicheIntelligenzzurAnomalieerkennung</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte (Consulting for requested firms)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Werkstudent AI &amp; Data Engineering</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>recruiting@company.com</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WerkstudentKünstlicheIntelligenzzurAnomalieerkennung</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WerkstudentSoftwareentwicklung</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>recruiting.ger@siemens.com</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WerkstudentSoftwareentwicklung</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WorkingStudentAdvancedAnalyticsandArtificialIntelligence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WorkingStudentAdvancedAnalyticsandArtificialIntelligence</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>data/raw_jds/WorkingStudentAdvancedAnalyticsandArtificialIntelligence.md</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WorkingStudentDataScientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WorkingStudentDataScientist</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>data/raw_jds/WorkingStudentDataScientist.md</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>docs/solutions/rejection_lessons.md</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WorkingStudentfmdFullStackSoftwareDevelopmentforInnovationProjects</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1019,122 +857,54 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unknown_Job</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Ready (Manual)</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WorkingStudentfmdFullStackSoftwareDevelopmentforInnovationProjects</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>data/raw_jds/WorkingStudentfmdFullStackSoftwareDevelopmentforInnovationProjects.md</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>WorkingStudentfmdLeveragingGenerativeAIalongtheSoftwareDevelopmentLifecycleSDLC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Siemens AG</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Ready (Manual)</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Siemens AG</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Working Student (f/m/d) Advanced Analytics and Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16">
-        <f>HYPERLINK("C:\Users\User\Jobs\data\tailored_outputs\WorkingStudentfmdAdvancedAnalyticsandArtificialIntelligence\Cover_Letter.pdf", "Letter")</f>
-        <v/>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Ready (Manual)</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Hiring Team</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16">
-        <f>HYPERLINK("C:\Users\User\Jobs\data\tailored_outputs\WorkingStudentfmdAdvancedAnalyticsandArtificialIntelligence\Tailored_CV.pdf", "PDF")</f>
-        <v/>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Tailored</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>data/tailored_outputs/WorkingStudentfmdLeveragingGenerativeAIalongtheSoftwareDevelopmentLifecycleSDLC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>data/raw_jds/WorkingStudentfmdLeveragingGenerativeAIalongtheSoftwareDevelopmentLifecycleSDLC.md</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
     </row>
